--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,47 +1378,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136970401</v>
+        <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>96784</v>
+        <v>97590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1429,10 +1421,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516294</v>
+        <v>516245</v>
       </c>
       <c r="R7" t="n">
-        <v>6633052</v>
+        <v>6633128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1478,22 +1470,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>dikad sumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1501,12 +1488,9 @@
           <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # Horizontal, dead with ground contact # murken låga # Picea abies</t>
+          <t>Horizontal, dead with ground contact # grov murken låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,53 +1511,45 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970401</t>
+          <t>https://artportalen.se/Sighting/137008408</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136970917</v>
+        <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>96784</v>
+        <v>97590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1584,10 +1560,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516248</v>
+        <v>516260</v>
       </c>
       <c r="R8" t="n">
-        <v>6633061</v>
+        <v>6633115</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1631,19 +1607,19 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>dikad sumpskog</t>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1651,9 +1627,12 @@
           <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov murken låga # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1674,13 +1653,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970917</t>
+          <t>https://artportalen.se/Sighting/137008479</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136970929</v>
+        <v>136970401</v>
       </c>
       <c r="B9" t="n">
         <v>96784</v>
@@ -1731,10 +1710,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516238</v>
+        <v>516294</v>
       </c>
       <c r="R9" t="n">
-        <v>6633072</v>
+        <v>6633052</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1778,6 +1757,11 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI9" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -1785,12 +1769,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1798,9 +1782,12 @@
           <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # murken låga # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1821,13 +1808,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970929</t>
+          <t>https://artportalen.se/Sighting/136970401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136971067</v>
+        <v>136970917</v>
       </c>
       <c r="B10" t="n">
         <v>96784</v>
@@ -1857,7 +1844,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1878,10 +1865,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516234</v>
+        <v>516248</v>
       </c>
       <c r="R10" t="n">
-        <v>6633117</v>
+        <v>6633061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1930,17 +1917,24 @@
           <t>dikad sumpskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr">
         <is>
           <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # Horizontal, dead with ground contact # grov murken låga</t>
+          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1961,47 +1955,56 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971067</t>
+          <t>https://artportalen.se/Sighting/136970917</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136970281</v>
+        <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>83455</v>
+        <v>96784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2009,10 +2012,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516227</v>
+        <v>516238</v>
       </c>
       <c r="R11" t="n">
-        <v>6632997</v>
+        <v>6633072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2047,11 +2050,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2061,14 +2059,9 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>dikad skog med vitmossor som dominerar bottenskiktet</t>
+          <t>dikad sumpskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2083,12 +2076,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # högstubbe, på basen # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2109,47 +2102,56 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970281</t>
+          <t>https://artportalen.se/Sighting/136970929</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136970947</v>
+        <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>83455</v>
+        <v>96784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2157,10 +2159,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516232</v>
+        <v>516234</v>
       </c>
       <c r="R12" t="n">
-        <v>6633080</v>
+        <v>6633117</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2209,19 +2211,9 @@
           <t>dikad sumpskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -2229,7 +2221,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # grov murken högstubbe # Betula pubescens</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov murken låga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2250,13 +2242,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970947</t>
+          <t>https://artportalen.se/Sighting/136971067</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136970963</v>
+        <v>136970281</v>
       </c>
       <c r="B13" t="n">
         <v>83455</v>
@@ -2298,10 +2290,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516244</v>
+        <v>516227</v>
       </c>
       <c r="R13" t="n">
-        <v>6633095</v>
+        <v>6632997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2336,6 +2328,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2345,9 +2342,14 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>dikad sumpskog</t>
+          <t>dikad skog med vitmossor som dominerar bottenskiktet</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2365,12 +2367,9 @@
           <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # på basen av grov murken högstubbe # Betula pubescens</t>
+          <t>Standing dead tree/snags # högstubbe, på basen # Betula pubescens</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2391,16 +2390,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970963</t>
+          <t>https://artportalen.se/Sighting/136970281</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136972123</v>
+        <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>81458</v>
+        <v>83455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2408,21 +2407,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2439,10 +2438,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516242</v>
+        <v>516232</v>
       </c>
       <c r="R14" t="n">
-        <v>6633155</v>
+        <v>6633080</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2488,17 +2487,17 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>dikad barrsumpskog</t>
+          <t>dikad sumpskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2506,9 +2505,12 @@
           <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # grovt torrträd intill djupt dike # Pinus sylvestris</t>
+          <t>1 substratenheter # Standing dead tree/snags # grov murken högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2529,48 +2531,47 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136972123</t>
+          <t>https://artportalen.se/Sighting/136970947</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136970312</v>
+        <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>96688</v>
+        <v>83455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2578,10 +2579,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516293</v>
+        <v>516244</v>
       </c>
       <c r="R15" t="n">
-        <v>6633066</v>
+        <v>6633095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2625,11 +2626,6 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -2647,12 +2643,15 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
+          <t>1 substratenheter # Standing dead tree/snags # på basen av grov murken högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2673,48 +2672,47 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970312</t>
+          <t>https://artportalen.se/Sighting/136970963</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136970471</v>
+        <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>96688</v>
+        <v>81458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2722,10 +2720,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516255</v>
+        <v>516242</v>
       </c>
       <c r="R16" t="n">
-        <v>6633050</v>
+        <v>6633155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2769,37 +2767,29 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>dikad sumpskog</t>
+          <t>dikad barrsumpskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>1</v>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # Horizontal, dead with ground contact # murken låga # Picea abies</t>
+          <t>Standing dead tree/snags # grovt torrträd intill djupt dike # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2820,13 +2810,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970471</t>
+          <t>https://artportalen.se/Sighting/136972123</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136970919</v>
+        <v>136970312</v>
       </c>
       <c r="B17" t="n">
         <v>96688</v>
@@ -2869,10 +2859,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516248</v>
+        <v>516293</v>
       </c>
       <c r="R17" t="n">
-        <v>6633061</v>
+        <v>6633066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2916,6 +2906,11 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI17" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -2959,13 +2954,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970919</t>
+          <t>https://artportalen.se/Sighting/136970312</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136970932</v>
+        <v>136970471</v>
       </c>
       <c r="B18" t="n">
         <v>96688</v>
@@ -2997,7 +2992,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -3008,10 +3003,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516238</v>
+        <v>516255</v>
       </c>
       <c r="R18" t="n">
-        <v>6633072</v>
+        <v>6633050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3055,6 +3050,11 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI18" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -3062,12 +3062,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3075,9 +3075,12 @@
           <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # murken låga # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3098,13 +3101,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970932</t>
+          <t>https://artportalen.se/Sighting/136970471</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136970994</v>
+        <v>136970919</v>
       </c>
       <c r="B19" t="n">
         <v>96688</v>
@@ -3136,7 +3139,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -3147,10 +3150,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>516249</v>
+        <v>516248</v>
       </c>
       <c r="R19" t="n">
-        <v>6633098</v>
+        <v>6633061</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3211,15 +3214,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # Stump # grov murken stubbe # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3240,13 +3240,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970994</t>
+          <t>https://artportalen.se/Sighting/136970919</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136972366</v>
+        <v>136970932</v>
       </c>
       <c r="B20" t="n">
         <v>96688</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516221</v>
+        <v>516238</v>
       </c>
       <c r="R20" t="n">
-        <v>6633120</v>
+        <v>6633072</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3333,7 +3333,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3359,7 +3358,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken låga invid djupt dike # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # grov murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3380,16 +3379,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136972366</t>
+          <t>https://artportalen.se/Sighting/136970932</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136970378</v>
+        <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>92338</v>
+        <v>96688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3397,34 +3396,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3432,10 +3428,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516307</v>
+        <v>516249</v>
       </c>
       <c r="R21" t="n">
-        <v>6633062</v>
+        <v>6633098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3479,11 +3475,6 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -3491,17 +3482,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -3509,7 +3500,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # på bas av mycket grov, murken högstubbe # Picea abies</t>
+          <t>1 substratenheter # Stump # grov murken stubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3530,16 +3521,16 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970378</t>
+          <t>https://artportalen.se/Sighting/136970994</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136970498</v>
+        <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>83446</v>
+        <v>96688</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3547,30 +3538,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>2818</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516283</v>
+        <v>516221</v>
       </c>
       <c r="R22" t="n">
-        <v>6633051</v>
+        <v>6633120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3622,14 +3614,10 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AI22" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -3647,15 +3635,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # murken högstubbe # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # murken låga invid djupt dike # Betula pubescens</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3676,16 +3661,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970498</t>
+          <t>https://artportalen.se/Sighting/136972366</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136972153</v>
+        <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>83446</v>
+        <v>92338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3693,30 +3678,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6439</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3724,10 +3713,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516206</v>
+        <v>516307</v>
       </c>
       <c r="R23" t="n">
-        <v>6633129</v>
+        <v>6633062</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3771,6 +3760,11 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI23" t="inlineStr">
         <is>
           <t>dikad sumpskog</t>
@@ -3778,12 +3772,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -3791,7 +3790,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>1 substratenheter # högstubbe # Betula pubescens</t>
+          <t>1 substratenheter # Standing dead tree/snags # på bas av mycket grov, murken högstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3812,50 +3811,45 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136972153</t>
+          <t>https://artportalen.se/Sighting/136970378</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136971214</v>
+        <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>58169</v>
+        <v>83446</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3865,13 +3859,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516280</v>
+        <v>516283</v>
       </c>
       <c r="R24" t="n">
-        <v>6632901</v>
+        <v>6633051</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3898,21 +3892,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3922,9 +3906,37 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
+          <t>dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Standing dead tree/snags # murken högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3945,50 +3957,45 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971214</t>
+          <t>https://artportalen.se/Sighting/136970498</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136971279</v>
+        <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>58169</v>
+        <v>83446</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3998,10 +4005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516330</v>
+        <v>516206</v>
       </c>
       <c r="R25" t="n">
-        <v>6632869</v>
+        <v>6633129</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4031,21 +4038,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4054,25 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
+          <t>dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4078,16 +4093,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971279</t>
+          <t>https://artportalen.se/Sighting/136972153</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136971319</v>
+        <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>58164</v>
+        <v>83446</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4095,33 +4110,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103023</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -4131,10 +4141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516330</v>
+        <v>516260</v>
       </c>
       <c r="R26" t="n">
-        <v>6632869</v>
+        <v>6633130</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4164,21 +4174,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4188,9 +4188,32 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Standing dead tree/snags # klen murken högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4211,16 +4234,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971319</t>
+          <t>https://artportalen.se/Sighting/137008430</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136970608</v>
+        <v>137008367</v>
       </c>
       <c r="B27" t="n">
-        <v>8452</v>
+        <v>5182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4228,21 +4251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4269,10 +4292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516220</v>
+        <v>516287</v>
       </c>
       <c r="R27" t="n">
-        <v>6633040</v>
+        <v>6633118</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4313,17 +4336,23 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>dikad sumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -4333,7 +4362,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torrträd</t>
+          <t>Standing dead tree/snags # torrträd med kvarsittande bark # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4354,71 +4383,66 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970608</t>
+          <t>https://artportalen.se/Sighting/137008367</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136970971</v>
+        <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>8452</v>
+        <v>58169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>516244</v>
+        <v>516280</v>
       </c>
       <c r="R28" t="n">
-        <v>6633095</v>
+        <v>6632901</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4445,11 +4469,21 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4461,27 +4495,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>dikad sumpskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov murken högstubbe # Betula pubescens</t>
+          <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4502,68 +4516,63 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970971</t>
+          <t>https://artportalen.se/Sighting/136971214</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136971004</v>
+        <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>8452</v>
+        <v>58169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>516246</v>
+        <v>516330</v>
       </c>
       <c r="R29" t="n">
-        <v>6633082</v>
+        <v>6632869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4593,11 +4602,21 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4609,27 +4628,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>dikad sumpskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov murken högstubbe # Betula pubescens</t>
+          <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4650,16 +4649,16 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971004</t>
+          <t>https://artportalen.se/Sighting/136971279</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136971852</v>
+        <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>8452</v>
+        <v>58164</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4667,51 +4666,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>516303</v>
+        <v>516330</v>
       </c>
       <c r="R30" t="n">
-        <v>6632879</v>
+        <v>6632869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4741,44 +4735,33 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
           <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # murken högstubbe och tillhörande låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4798,6 +4781,594 @@
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136971319</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136970608</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>516220</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6633040</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torrträd</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970608</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136970971</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516244</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6633095</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov murken högstubbe # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970971</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136971004</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>516246</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6633082</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov murken högstubbe # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136971004</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136971852</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västra Skogstorp, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>516303</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6632879</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>dikad, fuktig, grandominerad barrskog med inslag av glasbjörk och vitmossor som dominerar bottenskiktet</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # murken högstubbe och tillhörande låga # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136971852</t>
         </is>
@@ -4834,6 +5405,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81458</v>
+        <v>81462</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81462</v>
+        <v>81464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>136970608</v>
       </c>
       <c r="B31" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>136970971</v>
       </c>
       <c r="B32" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>136971004</v>
       </c>
       <c r="B33" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136971852</v>
       </c>
       <c r="B34" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -854,11 +850,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -989,11 +981,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1131,11 +1119,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1273,11 +1257,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1408,11 +1388,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1547,11 +1523,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1697,11 +1669,7 @@
           <t>kapslar</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1852,11 +1820,7 @@
           <t>kapslar</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1999,11 +1963,7 @@
           <t>kapslar</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -2146,11 +2106,7 @@
           <t>kapslar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2278,11 +2234,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2426,11 +2378,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2567,11 +2515,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2708,11 +2652,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2846,11 +2786,7 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2990,11 +2926,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -3137,11 +3069,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -3276,11 +3204,7 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -3415,11 +3339,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -3557,11 +3477,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3847,11 +3763,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3993,11 +3905,7 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4129,11 +4037,7 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4270,17 +4174,9 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4424,11 +4320,7 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4557,11 +4449,7 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4690,11 +4578,7 @@
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4818,17 +4702,9 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4961,17 +4837,9 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5109,17 +4977,9 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5257,17 +5117,9 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>137008367</v>
       </c>
       <c r="B27" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>136970608</v>
       </c>
       <c r="B31" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136970971</v>
       </c>
       <c r="B32" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>136971004</v>
       </c>
       <c r="B33" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>136971852</v>
       </c>
       <c r="B34" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96865</v>
+        <v>96866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96865</v>
+        <v>96866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96865</v>
+        <v>96866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96865</v>
+        <v>96866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83518</v>
+        <v>83519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83518</v>
+        <v>83519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83518</v>
+        <v>83519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81504</v>
+        <v>81505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83509</v>
+        <v>83510</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83509</v>
+        <v>83510</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83509</v>
+        <v>83510</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37643-2026 artfynd.xlsx
+++ b/artfynd/A 37643-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136970311</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136971122</v>
       </c>
       <c r="B3" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>136972223</v>
       </c>
       <c r="B4" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>136972331</v>
       </c>
       <c r="B5" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136972412</v>
       </c>
       <c r="B6" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137008408</v>
       </c>
       <c r="B7" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>137008479</v>
       </c>
       <c r="B8" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136970401</v>
       </c>
       <c r="B9" t="n">
-        <v>96866</v>
+        <v>96869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136970917</v>
       </c>
       <c r="B10" t="n">
-        <v>96866</v>
+        <v>96869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136970929</v>
       </c>
       <c r="B11" t="n">
-        <v>96866</v>
+        <v>96869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>136971067</v>
       </c>
       <c r="B12" t="n">
-        <v>96866</v>
+        <v>96869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136970281</v>
       </c>
       <c r="B13" t="n">
-        <v>83519</v>
+        <v>83522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>136970947</v>
       </c>
       <c r="B14" t="n">
-        <v>83519</v>
+        <v>83522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136970963</v>
       </c>
       <c r="B15" t="n">
-        <v>83519</v>
+        <v>83522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136972123</v>
       </c>
       <c r="B16" t="n">
-        <v>81505</v>
+        <v>81508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136970312</v>
       </c>
       <c r="B17" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136970471</v>
       </c>
       <c r="B18" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>136970919</v>
       </c>
       <c r="B19" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>136970932</v>
       </c>
       <c r="B20" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136970994</v>
       </c>
       <c r="B21" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136972366</v>
       </c>
       <c r="B22" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136970378</v>
       </c>
       <c r="B23" t="n">
-        <v>92411</v>
+        <v>92414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>136970498</v>
       </c>
       <c r="B24" t="n">
-        <v>83510</v>
+        <v>83513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136972153</v>
       </c>
       <c r="B25" t="n">
-        <v>83510</v>
+        <v>83513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>137008430</v>
       </c>
       <c r="B26" t="n">
-        <v>83510</v>
+        <v>83513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>136971214</v>
       </c>
       <c r="B28" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136971279</v>
       </c>
       <c r="B29" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136971319</v>
       </c>
       <c r="B30" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
